--- a/jpcore-r4b/develop/StructureDefinition-jp-medicationstatement-injection.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-medicationstatement-injection.xlsx
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) (http://jpfhir.jp, office@hlfhir.jp)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/jpcore-r4b/develop/StructureDefinition-jp-medicationstatement-injection.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-medicationstatement-injection.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1335" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1335" uniqueCount="331">
   <si>
     <t>Property</t>
   </si>
@@ -1057,13 +1057,16 @@
 </t>
   </si>
   <si>
-    <t>薬の服用方法・服用した方法、または服用すべき方法</t>
+    <t>Details of how medication is/was taken or should be taken</t>
+  </si>
+  <si>
+    <t>Indicates how the medication is/was or should be taken by the patient.</t>
   </si>
   <si>
     <t>The dates included in the dosage on a Medication Statement reflect the dates for a given dose.  For example, "from November 1, 2016 to November 3, 2016, take one tablet daily and from November 4, 2016 to November 7, 2016, take two tablets daily."  It is expected that this specificity may only be populated where the patient brings in their labeled container or where the Medication Statement is derived from a MedicationRequest.</t>
   </si>
   <si>
-    <t>.outboundRelationship[typeCode=COMP].target[classCode=SBADM, moodCode=INT]</t>
+    <t>refer dosageInstruction mapping</t>
   </si>
 </sst>
 </file>
@@ -5437,10 +5440,10 @@
         <v>327</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5508,7 +5511,7 @@
         <v>79</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>79</v>

--- a/jpcore-r4b/develop/StructureDefinition-jp-medicationstatement-injection.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-medicationstatement-injection.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev-temp</t>
+    <t>2.0.0-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4b/develop/StructureDefinition-jp-medicationstatement-injection.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-medicationstatement-injection.xlsx
@@ -271,7 +271,16 @@
     <t>患者が薬剤を服用している状況についての情報である。</t>
   </si>
   <si>
-    <t>When interpreting a medicationStatement, the value of the status and NotTaken needed to be considered:+    <t>薬物測定を解釈するとき、ステータスの価値とNottakenを考慮する必要があります。+dedicationStatement.status + decutionStatement.wasnottaken+ステータス=アクティブ + nottaken = t =現在取得していない+ステータス=完了 + nottaken = t =過去に撮影されていない+status = dented + nottaken = t =取得する意図はありません+ステータス=アクティブ + nottaken = f =撮影ですが、規定されていない+ステータス=アクティブ + nottaken = f =撮影+status = dented +nottaken = f =は取得されます（開始されません）+ステータス=完了 + nottaken = f =過去に撮影+status = in error + nottaken = n/a =エラー。 / When interpreting a medicationStatement, the value of the status and NotTaken needed to be considered: MedicationStatement.status + MedicationStatement.wasNotTaken Status=Active + NotTaken=T = Not currently taking Status=Completed + NotTaken=T = Not taken in the past@@ -283,8 +292,8 @@
 Status=In Error + NotTaken=N/A = In Error.</t>
   </si>
   <si>
-    <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+    <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -309,13 +318,13 @@
 </t>
   </si>
   <si>
-    <t>Logical id of this artifact</t>
-  </si>
-  <si>
-    <t>The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
-  </si>
-  <si>
-    <t>The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
+    <t>このアーティファクトの論理ID / Logical id of this artifact</t>
+  </si>
+  <si>
+    <t>リソースのURLで使用されるリソースの論理ID。割り当てられたら、この値は変更されません。 / The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
+  </si>
+  <si>
+    <t>リソースにIDがないのは、IDが作成操作を使用してサーバーに送信されている場合です。 / The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -328,16 +337,16 @@
 </t>
   </si>
   <si>
-    <t>Metadata about the resource</t>
-  </si>
-  <si>
-    <t>The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -348,13 +357,13 @@
 </t>
   </si>
   <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+    <t>このコンテンツが作成されたルールのセット / A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>リソースが構築されたときに従った一連のルールへの参照。コンテンツの処理時に理解する必要があります。多くの場合、これは他のプロファイルなどとともに特別なルールを定義する実装ガイドへの参照です。 / A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>このルールセットを主張することは、コンテンツが限られた取引パートナーのセットによってのみ理解されることを制限します。これにより、本質的に長期的にデータの有用性が制限されます。ただし、既存の健康エコシステムは非常に破壊されており、一般的に計算可能な意味でデータを定義、収集、交換する準備ができていません。可能な限り、実装者や仕様ライターはこの要素の使用を避ける必要があります。多くの場合、使用する場合、URLは、これらの特別なルールを他のプロファイル、バリューセットなどとともに叙述(Narative)の一部として定義する実装ガイドへの参照です。 / Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
   </si>
   <si>
     <t>Resource.implicitRules</t>
@@ -367,19 +376,19 @@
 </t>
   </si>
   <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+    <t>リソースコンテンツの言語 / Language of the resource content</t>
+  </si>
+  <si>
+    <t>リソースが書かれている基本言語。 / The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>言語は、インデックス作成とアクセシビリティをサポートするために提供されます（通常、テキストから音声までのサービスなどのサービスが言語タグを使用します）。叙述(Narative)のHTML言語タグは、叙述(Narative)に適用されます。リソース上の言語タグを使用して、リソース内のデータから生成された他のプレゼンテーションの言語を指定できます。すべてのコンテンツが基本言語である必要はありません。リソース。言語は、叙述(Narative)に自動的に適用されると想定されるべきではありません。言語が指定されている場合、HTMLのDIV要素にも指定されている場合（XML：LangとHTML Lang属性の関係については、HTML5のルールを参照してください）。 / Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
   </si>
   <si>
     <t>preferred</t>
   </si>
   <si>
-    <t>IETF language tag</t>
+    <t>IETF言語タグ / IETF language tag</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages|4.3.0</t>
@@ -399,13 +408,13 @@
 </t>
   </si>
   <si>
-    <t>Text summary of the resource, for human interpretation</t>
-  </si>
-  <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+    <t>人間の解釈のためのリソースのテキスト概要 / Text summary of the resource, for human interpretation</t>
+  </si>
+  <si>
+    <t>リソースの概要を含み、人間へのリソースの内容を表すために使用できる人間の読み取り可能な叙述(Narative)。叙述(Narative)はすべての構造化されたデータをエンコードする必要はありませんが、人間が叙述(Narative)を読むだけで「臨床的に安全」にするために十分な詳細を含める必要があります。リソースの定義は、臨床的安全を確保するために、叙述(Narative)で表現するコンテンツを定義する場合があります。 / A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>含まれるリソースには叙述(Narative)がありません。含まれていないリソースには叙述(Narative)が必要です。場合によっては、リソースには、追加の個別のデータがほとんどまたはまったくないテキストのみがあります（すべてのMinoccur = 1要素が満たされている限り）。これは、情報がtext blob (バイナリー ラージ オブジェクト)としてキャプチャされるレガシーシステムからのデータ、またはテキストが生またはナレーションされ、エンコードされた情報が後で追加される場合に必要になる場合があります。 / Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
   </si>
   <si>
     <t>DomainResource.text</t>
@@ -425,19 +434,19 @@
 </t>
   </si>
   <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+    <t>インラインリソースが含まれています / Contained, inline Resources</t>
+  </si>
+  <si>
+    <t>これらのリソースには、それらを含むリソースを除いて独立した存在はありません - 独立して特定することはできず、独自の独立したトランザクションスコープを持つこともできません。 / These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>識別が失われると、コンテンツを適切に識別できる場合は、これを行うべきではありません。含まれるリソースには、メタ要素にプロファイルとタグがある場合がありますが、セキュリティラベルはありません。 / This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
+    <t xml:space="preserve">dom-r4b:R4リソース内に新しいR4Bリソースを含めると、インスタンスがR4システムと共有された場合に相互運用性の問題が発生する可能性があります / Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
 </t>
   </si>
   <si>
@@ -455,33 +464,34 @@
 </t>
   </si>
   <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+    <t>実装で定義された追加のコンテンツ / Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>リソースの基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>拡張機能を使用または定義する機関や管轄権に関係なく、アプリケーション、プロジェクト、または標準による拡張機能の使用に関連するスティグマはありません。拡張機能の使用は、FHIR仕様がすべての人にコアレベルのシンプルさを保持できるようにするものです。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>MedicationStatement.modifierExtension</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>無視できない拡張機能 / Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>リソースの基本的な定義の一部ではなく、それを含む要素の理解および/または含有要素の子孫の理解を変更するために使用される場合があります。通常、修飾子要素は否定または資格を提供します。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たされる一連の要件があります。アプリケーションの処理リソースは、修飾子拡張機能をチェックする必要があります。
+モディファイア拡張は、リソースまたはdomainResource上の要素の意味を変更してはなりません（修飾軸自体の意味を変更することはできません）。 / May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
+    <t>修飾子拡張機能により、安全に無視できる大部分の拡張機能と明確に区別できるように、安全に無視できない拡張機能が可能になります。これにより、実装者が拡張の存在を禁止する必要性を排除することにより、相互運用性が促進されます。詳細については、[修飾子拡張の定義]（拡張性.html＃modifierextension）を参照してください。 / Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -520,13 +530,13 @@
 </t>
   </si>
   <si>
-    <t>Fulfils plan, proposal or order</t>
-  </si>
-  <si>
-    <t>A plan, proposal or order that is fulfilled in whole or in part by this event.</t>
-  </si>
-  <si>
-    <t>Allows tracing of authorization for the event and tracking whether proposals/recommendations were acted upon.</t>
+    <t>計画、提案、または命令を満たします / Fulfils plan, proposal or order</t>
+  </si>
+  <si>
+    <t>このイベントによって全体または一部に満たされる計画、提案、または命令。 / A plan, proposal or order that is fulfilled in whole or in part by this event.</t>
+  </si>
+  <si>
+    <t>イベントの許可を追跡し、提案/勧告が行われたかどうかを追跡することができます。 / Allows tracing of authorization for the event and tracking whether proposals/recommendations were acted upon.</t>
   </si>
   <si>
     <t>Event.basedOn</t>
@@ -542,13 +552,13 @@
 </t>
   </si>
   <si>
-    <t>Part of referenced event</t>
-  </si>
-  <si>
-    <t>A larger event of which this particular event is a component or step.</t>
-  </si>
-  <si>
-    <t>This should not be used when indicating which resource a MedicationStatement has been derived from.  If that is the use case, then MedicationStatement.derivedFrom should be used.</t>
+    <t>参照イベントの一部 / Part of referenced event</t>
+  </si>
+  <si>
+    <t>この特定のイベントがコンポーネントまたはステップであるより大きなイベント。 / A larger event of which this particular event is a component or step.</t>
+  </si>
+  <si>
+    <t>これは、薬物測定がどのリソースから導出されているかを示す場合は使用しないでください。それがユースケースである場合、secticationStatement.derivedfromを使用する必要があります。 / This should not be used when indicating which resource a MedicationStatement has been derived from.  If that is the use case, then MedicationStatement.derivedFrom should be used.</t>
   </si>
   <si>
     <t>Event.partOf</t>
@@ -560,7 +570,7 @@
     <t>MedicationStatement.status</t>
   </si>
   <si>
-    <t>active | completed | entered-in-error | intended | stopped | on-hold | unknown | not-taken</t>
+    <t>アクティブ | 完了 | エラー入力 | 意図的 | 停止 | 保留 | 不明 | 未取得 / active | completed | entered-in-error | intended | stopped | on-hold | unknown | not-taken</t>
   </si>
   <si>
     <t>服薬状況のを示す。コード表： http://hl7.org/fhir/CodeSystem/medication-statement-status
@@ -573,7 +583,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>A coded concept indicating the current status of a MedicationStatement.</t>
+    <t>薬剤の現在の状態を示すコード化された概念。 / A coded concept indicating the current status of a MedicationStatement.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/medication-statement-status|4.3.0</t>
@@ -607,7 +617,7 @@
     <t>example</t>
   </si>
   <si>
-    <t>A coded concept indicating the reason for the status of the statement.</t>
+    <t>ステートメントのステータスの理由を示すコード化された概念。 / A coded concept indicating the reason for the status of the statement.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/reason-medication-status-codes|4.3.0</t>
@@ -631,7 +641,7 @@
 HL7 FHIRではvalue setとして http://terminology.hl7.org/CodeSystem/medicationrequest-category がデフォルトで用いられるが、日本での使用の場合持参薬をカバーする必要があり、JAHIS処方データ規約V3.0Cに記載されているMERIT-9処方オーダ表7とJHSP0007表を組み合わせて持ちいることとする</t>
   </si>
   <si>
-    <t>A coded concept identifying where the medication included in the MedicationStatement is expected to be consumed or administered.</t>
+    <t>薬剤が含まれている場所を識別するコード化された概念は、薬物測定に含まれる場所が消費または投与されると予想されます。 / A coded concept identifying where the medication included in the MedicationStatement is expected to be consumed or administered.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/medication-statement-category|4.3.0</t>
@@ -713,10 +723,10 @@
 </t>
   </si>
   <si>
-    <t>Encounter / Episode associated with MedicationStatement</t>
-  </si>
-  <si>
-    <t>The encounter or episode of care that establishes the context for this MedicationStatement.</t>
+    <t>MedicationStatementに関連するEncounter / Episode / Encounter / Episode associated with MedicationStatement</t>
+  </si>
+  <si>
+    <t>この薬物測定のコンテキストを確立するEnounterまたはケアのエピソード。 / The encounter or episode of care that establishes the context for this MedicationStatement.</t>
   </si>
   <si>
     <t>Event.context</t>
@@ -732,13 +742,13 @@
 Period</t>
   </si>
   <si>
-    <t>The date/time or interval when the medication is/was/will be taken</t>
-  </si>
-  <si>
-    <t>The interval of time during which it is being asserted that the patient is/was/will be taking the medication (or was not taking, when the MedicationStatement.taken element is No).</t>
-  </si>
-  <si>
-    <t>This attribute reflects the period over which the patient consumed the medication and is expected to be populated on the majority of Medication Statements. If the medication is still being taken at the time the statement is recorded, the "end" date will be omitted.  The date/time attribute supports a variety of dates - year, year/month and exact date.  If something more than this is required, this should be conveyed as text.</t>
+    <t>薬が服用/服用/服用/時刻または間隔 / The date/time or interval when the medication is/was/will be taken</t>
+  </si>
+  <si>
+    <t>患者が薬を服用している/服用している/（または薬を服用していなかった）と主張されている時間の間隔。 / The interval of time during which it is being asserted that the patient is/was/will be taking the medication (or was not taking, when the MedicationStatement.taken element is No).</t>
+  </si>
+  <si>
+    <t>この属性は、患者が投薬を消費した期間を反映しており、投薬声明の大部分に埋め込むことが期待されています。声明が記録された時点で薬がまだ撮影されている場合、「終了」日付は省略されます。日付/時刻属性は、年、年/月、正確な日付のさまざまな日付をサポートしています。これ以上のものが必要な場合は、これをテキストとして伝える必要があります。 / This attribute reflects the period over which the patient consumed the medication and is expected to be populated on the majority of Medication Statements. If the medication is still being taken at the time the statement is recorded, the "end" date will be omitted.  The date/time attribute supports a variety of dates - year, year/month and exact date.  If something more than this is required, this should be conveyed as text.</t>
   </si>
   <si>
     <t xml:space="preserve">type:$this}
@@ -779,10 +789,10 @@
     <t>MedicationStatement.effective[x].id</t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+    <t>要素間参照のための一意のID / Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>リソース内の要素の一意のID（内部参照用）。これは、スペースを含まない文字列値である場合があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
   </si>
   <si>
     <t>Element.id</t>
@@ -797,7 +807,7 @@
     <t>MedicationStatement.effective[x].extension</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+    <t>要素の基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t xml:space="preserve">value:url}
@@ -826,7 +836,7 @@
     <t>薬の服用を開始した日</t>
   </si>
   <si>
-    <t>If the low element is missing, the meaning is that the low boundary is not known.</t>
+    <t>低要素が欠落している場合、意味は低い境界が知られていないことです。 / If the low element is missing, the meaning is that the low boundary is not known.</t>
   </si>
   <si>
     <t>Period.start</t>
@@ -857,7 +867,7 @@
     <t>この値は必ず境界日を含む。2012-02-03T10:00:00は2012-02-03を終了時刻(end)の値とする期間を示す。</t>
   </si>
   <si>
-    <t>If the end of the period is missing, it means that the period is ongoing</t>
+    <t>期間の終了が欠落している場合、それは期間が進行中であることを意味します / If the end of the period is missing, it means that the period is ongoing</t>
   </si>
   <si>
     <t>Period.end</t>
@@ -913,7 +923,7 @@
     <t>MedicationStatementリソースと関連するMedicationRequestやその他の支持情報を表すリソースと関連付けられるようにする。</t>
   </si>
   <si>
-    <t>Likely references would be to MedicationRequest, MedicationDispense, Claim, Observation or QuestionnaireAnswers.  The most common use cases for deriving a MedicationStatement comes from creating a MedicationStatement from a MedicationRequest or from a lab observation or a claim.  it should be noted that the amount of information that is available varies from the type resource that you derive the MedicationStatement from.</t>
+    <t>おそらく参考文献は、薬物療法、薬剤、請求、観察、またはアンケート担当者に関するものです。薬物測定を導き出すための最も一般的なユースケースは、薬物療法または実験室の観察または請求からの薬物測定の作成に由来しています。利用可能な情報の量は、投薬手段を導き出すタイプリソースから異なることに注意する必要があります。 / Likely references would be to MedicationRequest, MedicationDispense, Claim, Observation or QuestionnaireAnswers.  The most common use cases for deriving a MedicationStatement comes from creating a MedicationStatement from a MedicationRequest or from a lab observation or a claim.  it should be noted that the amount of information that is available varies from the type resource that you derive the MedicationStatement from.</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=SPRT]/target[classCode=ACT,moodCode=EVN]</t>
@@ -931,7 +941,7 @@
     <t>このコードは疾患分類であっても良い。JP Coreでは傷病名マスターの使用を前提とする。</t>
   </si>
   <si>
-    <t>A coded concept identifying why the medication is being taken.</t>
+    <t>薬が服用されている理由を特定するコード化された概念。 / A coded concept identifying why the medication is being taken.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/condition-code|4.3.0</t>
@@ -962,13 +972,13 @@
     <t>投与理由，対象疾患についてのコード</t>
   </si>
   <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+    <t>用語システムによって定義されたコードへの参照。 / A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>コードは、列挙されたCTなどの非常に正式な定義まで、列挙またはコードリストで非常にさりげなく定義される場合があります。詳細については、HL7 V3コアプリンシップを参照してください。コーディングの順序付けは未定義であり、意味を推測するために使用されません。一般に、せいぜい、コーディング値の1つのみがuserselected = trueとしてラベル付けされます。 / Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>コードシステム内の代替エンコーディング、および他のコードシステムへの翻訳が可能になります。 / Allows for alternative encodings within a code system, and translations to other code systems.</t>
   </si>
   <si>
     <t>CodeableConcept.coding</t>
@@ -987,16 +997,16 @@
 </t>
   </si>
   <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+    <t>コンセプトの単純なテキスト表現 / Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>データを入力したユーザー、および/またはユーザーの意図された意味を表すユーザーによって見られる/選択/発言された概念の人間の言語表現。 / A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>多くの場合、テキストはコーディングの1つの表示名と同じです。 / Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>用語からのコードは、それらを使用する人間のすべてのニュアンスを使用して、常に正しい意味をキャプチャするとは限りません。または、適切なコードがまったくない場合があります。これらの場合、テキストはソースの完全な意味をキャプチャするために使用されます。 / The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
   </si>
   <si>
     <t>CodeableConcept.text</t>
@@ -1018,10 +1028,10 @@
     <t>服薬理由を支持するObservation, Condition, DiagnosticReportについての参照。</t>
   </si>
   <si>
-    <t>Condition or observation that supports why the medication is being/was taken.</t>
-  </si>
-  <si>
-    <t>This is a reference to a condition that is the reason why the medication is being/was taken.  If only a code exists, use reasonForUseCode.</t>
+    <t>薬が摂取されている理由をサポートする状態または観察。 / Condition or observation that supports why the medication is being/was taken.</t>
+  </si>
+  <si>
+    <t>これは、薬が服用されている/服用されている理由である状態への言及です。コードのみが存在する場合は、ReasonForUseCodeを使用してください。 / This is a reference to a condition that is the reason why the medication is being/was taken.  If only a code exists, use reasonForUseCode.</t>
   </si>
   <si>
     <t>Event.reasonReference</t>
@@ -1062,7 +1072,7 @@
     <t>患者にこの薬剤がどのように服用すべきかを示す情報</t>
   </si>
   <si>
-    <t>The dates included in the dosage on a Medication Statement reflect the dates for a given dose.  For example, "from November 1, 2016 to November 3, 2016, take one tablet daily and from November 4, 2016 to November 7, 2016, take two tablets daily."  It is expected that this specificity may only be populated where the patient brings in their labeled container or where the Medication Statement is derived from a MedicationRequest.</t>
+    <t>投薬声明の投与量に含まれる日付は、特定の用量の日付を反映しています。たとえば、「2016年11月1日から2016年11月3日まで、毎日1錠を服用し、2016年11月4日から2016年11月7日まで、毎日2錠を服用してください。」この特異性は、患者が標識容器を持ち込む場合、または薬物療法の声明が薬物療法に由来する場合にのみ居住することが予想されます。 / The dates included in the dosage on a Medication Statement reflect the dates for a given dose.  For example, "from November 1, 2016 to November 3, 2016, take one tablet daily and from November 4, 2016 to November 7, 2016, take two tablets daily."  It is expected that this specificity may only be populated where the patient brings in their labeled container or where the Medication Statement is derived from a MedicationRequest.</t>
   </si>
   <si>
     <t>refer dosageInstruction mapping</t>
@@ -1161,10 +1171,11 @@
 user contentmodifiers</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>認識されていなくても無視できない拡張機能 / Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義の一部ではなく、それが含まれている要素の理解、および/または含まれる要素の子孫の理解を変更するために使用される場合があります。通常、修飾子要素は否定または資格を提供します。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。アプリケーションの処理リソースは、修飾子拡張機能をチェックする必要があります。
+モディファイア拡張は、リソースまたはdomainResource上の要素の意味を変更してはなりません（修飾軸自体の意味を変更することはできません）。 / May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
@@ -1272,10 +1283,10 @@
     <t>投与タイミングを記録する。</t>
   </si>
   <si>
-    <t>This attribute might not always be populated while the Dosage.text is expected to be populated.  If both are populated, then the Dosage.text should reflect the content of the Dosage.timing.</t>
-  </si>
-  <si>
-    <t>The timing schedule for giving the medication to the patient. This  data type allows many different expressions. For example: "Every 8 hours"; "Three times a day"; "1/2 an hour before breakfast for 10 days from 23-Dec 2011:"; "15 Oct 2013, 17 Oct 2013 and 1 Nov 2013".  Sometimes, a rate can imply duration when expressed as total volume / duration (e.g.  500mL/2 hours implies a duration of 2 hours).  However, when rate doesn't imply duration (e.g. 250mL/hour), then the timing.repeat.duration is needed to convey the infuse over time period.</t>
+    <t>この属性は、Dosage.Textが入力されると予想される間、常に埋め込まれるとは限りません。両方が入力されている場合、Dosage.textはDosage.timingの内容を反映する必要があります。 / This attribute might not always be populated while the Dosage.text is expected to be populated.  If both are populated, then the Dosage.text should reflect the content of the Dosage.timing.</t>
+  </si>
+  <si>
+    <t>患者への薬剤投与のタイミングスケジュール。このデータ型は多くの異なる表現を許可します。例えば：「8時間ごと」、「1日3回」、「2011年12月23日から10日間、朝食の30分前」、「2013年10月15日、2013年10月17日、2013年11月1日」。場合によっては、速度が総量/期間として表現される場合、期間を暗示することがあります（例：500mL/2時間は2時間の期間を暗示）。ただし、速度が期間を暗示しない場合（例：250mL/時間）、timing.repeat.durationが注入期間を伝えるために必要です。 / The timing schedule for giving the medication to the patient. This  data type allows many different expressions. For example: "Every 8 hours"; "Three times a day"; "1/2 an hour before breakfast for 10 days from 23-Dec 2011:"; "15 Oct 2013, 17 Oct 2013 and 1 Nov 2013".  Sometimes, a rate can imply duration when expressed as total volume / duration (e.g.  500mL/2 hours implies a duration of 2 hours).  However, when rate doesn't imply duration (e.g. 250mL/hour), then the timing.repeat.duration is needed to convey the infuse over time period.</t>
   </si>
   <si>
     <t>Dosage.timing</t>
@@ -1299,7 +1310,7 @@
     <t>服用タイミングを具体的な日時で指定する場合に使用する</t>
   </si>
   <si>
-    <t>In a Medication Administration Record, for instance, you need to take a general specification, and turn it into a precise specification.</t>
+    <t>たとえば、投薬投与の記録では、一般的な仕様を取得し、それを正確な仕様に変える必要があります。 / In a Medication Administration Record, for instance, you need to take a general specification, and turn it into a precise specification.</t>
   </si>
   <si>
     <t>Timing.event</t>
@@ -1327,8 +1338,8 @@
     <t>Timing.repeat</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-tim-1:if there's a duration, there needs to be duration units {duration.empty() or durationUnit.exists()}tim-2:if there's a period, there needs to be period units {period.empty() or periodUnit.exists()}tim-4:duration SHALL be a non-negative value {duration.exists() implies duration &gt;= 0}tim-5:period SHALL be a non-negative value {period.exists() implies period &gt;= 0}tim-6:If there's a periodMax, there must be a period {periodMax.empty() or period.exists()}tim-7:If there's a durationMax, there must be a duration {durationMax.empty() or duration.exists()}tim-8:If there's a countMax, there must be a count {countMax.empty() or count.exists()}tim-9:If there's an offset, there must be a when (and not C, CM, CD, CV) {offset.empty() or (when.exists() and ((when in ('C' | 'CM' | 'CD' | 'CV')).not()))}tim-10:If there's a timeOfDay, there cannot be a when, or vice versa {timeOfDay.empty() or when.empty()}</t>
+    <t>ele-1:空のParametersリソースでない限り、すべてのFHIR要素には@valueまたはchildrenが必要です / All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+tim-1:期間がある場合は、期間単位が必要です / if there's a duration, there needs to be duration units {duration.empty() or durationUnit.exists()}tim-2:期間がある場合、期間単位が必要です / if there's a period, there needs to be period units {period.empty() or periodUnit.exists()}tim-4:期間は非陰性価値です / duration SHALL be a non-negative value {duration.exists() implies duration &gt;= 0}tim-5:期間は非陰性の価値です / period SHALL be a non-negative value {period.exists() implies period &gt;= 0}tim-6:期間がある場合、期間がなければなりません / If there's a periodMax, there must be a period {periodMax.empty() or period.exists()}tim-7:Hurtermaxがある場合、期間がなければなりません / If there's a durationMax, there must be a duration {durationMax.empty() or duration.exists()}tim-8:countmaxがある場合、カウントが必要です / If there's a countMax, there must be a count {countMax.empty() or count.exists()}tim-9:オフセットがある場合、c、cm、cd、cvではなく（c、cvではない）存在する必要があります。 / If there's an offset, there must be a when (and not C, CM, CD, CV) {offset.empty() or (when.exists() and ((when in ('C' | 'CM' | 'CD' | 'CV')).not()))}tim-10:時間がある場合、いつ、またはその逆もありません / If there's a timeOfDay, there cannot be a when, or vice versa {timeOfDay.empty() or when.empty()}</t>
   </si>
   <si>
     <t>Implies PIVL or EIVL</t>
@@ -1375,7 +1386,7 @@
     <t>回数に上限、下限の範囲がある場合は、このcountで示される回数が起きるまでは、エレメントは範囲の中にあると解釈されるべきである。</t>
   </si>
   <si>
-    <t>Repetitions may be limited by end time or total occurrences.</t>
+    <t>繰り返しは、終了時間または合計発生によって制限される場合があります。 / Repetitions may be limited by end time or total occurrences.</t>
   </si>
   <si>
     <t>Timing.repeat.count</t>
@@ -1439,7 +1450,7 @@
     <t>MedicationStatement.dosage.timing.repeat.durationUnit</t>
   </si>
   <si>
-    <t>s | min | h | d | wk | mo | a - unit of time (UCUM)</t>
+    <t>s |min |h |d |wk |mo |A-時間単位（ucum） / s | min | h | d | wk | mo | a - unit of time (UCUM)</t>
   </si>
   <si>
     <t>UCUM単位で表される継続時間についての単位。</t>
@@ -1466,7 +1477,7 @@
     <t>32ビットの数値。もし、値がそれを上回るようであればdecimalを使用する。</t>
   </si>
   <si>
-    <t>If no frequency is stated, the assumption is that the event occurs once per period, but systems SHOULD always be specific about this</t>
+    <t>頻度が記載されていない場合、イベントは期間ごとに1回発生するという仮定ですが、システムは常にこれについて具体的でなければなりません / If no frequency is stated, the assumption is that the event occurs once per period, but systems SHOULD always be specific about this</t>
   </si>
   <si>
     <t>Timing.repeat.frequency</t>
@@ -1526,7 +1537,7 @@
     <t>MedicationStatement.dosage.timing.repeat.dayOfWeek</t>
   </si>
   <si>
-    <t>mon | tue | wed | thu | fri | sat | sun</t>
+    <t>月|火|水|木|金|土|太陽 / mon | tue | wed | thu | fri | sat | sun</t>
   </si>
   <si>
     <t>期間として1週間以上が指定されていれば、指定された曜日のみで投与が行われる。</t>
@@ -1606,7 +1617,7 @@
     <t>MedicationStatement.dosage.timing.code</t>
   </si>
   <si>
-    <t>BID | TID | QID | AM | PM | QD | QOD | +</t>
+    <t>入札|TID |QID |AM |PM |QD |qod |+ / BID | TID | QID | AM | PM | QD | QOD | +</t>
   </si>
   <si>
     <t>スケジュール上のタイミングを表すコード（あるいはcode.text内のテキスト）。BID(1日2回)のようなコードはどこにでもあるが、多くの医療機関は付加的なコードを定義している。もし、コードが示されていれば、構造化されたタイミングで完全に示されたデータであると解釈され、コードまたはTimingを解釈するためのデータであると解釈される。しかし、例外的に.repeat.bounds（コードは含まれない)はコードを上書きして適用される。</t>
@@ -1639,7 +1650,7 @@
 Medication(薬剤)が必要なときに指定された量とスケジュールのみで投薬するか（Booleanで選択される）、投薬する前提条件はTiming.Code(CodeableConcept)を示している。</t>
   </si>
   <si>
-    <t>Can express "as needed" without a reason by setting the Boolean = True.  In this case the CodeableConcept is not populated.  Or you can express "as needed" with a reason by including the CodeableConcept.  In this case the Boolean is assumed to be True.  If you set the Boolean to False, then the dose is given according to the schedule and is not "prn" or "as needed".</t>
+    <t>boolean = trueを設定することにより、理由なしに「必要に応じて」表現できます。この場合、codeableconceptは存在しません。または、Codeableconceptを含めることにより、「必要に応じて」理由で「必要に応じて」表現することができます。この場合、ブール値は真であると想定されています。ブール値をfalseに設定すると、用量はスケジュールに従って与えられ、「PRN」または「必要に応じて」ではありません。 / Can express "as needed" without a reason by setting the Boolean = True.  In this case the CodeableConcept is not populated.  Or you can express "as needed" with a reason by including the CodeableConcept.  In this case the Boolean is assumed to be True.  If you set the Boolean to False, then the dose is given according to the schedule and is not "prn" or "as needed".</t>
   </si>
   <si>
     <t>Dosage.asNeeded[x]</t>
@@ -1664,7 +1675,7 @@
 【JP Core仕様】JAMI外用部位３桁コードを使用することが望ましいが、ローカルコードも使用可能。</t>
   </si>
   <si>
-    <t>A coded specification of the anatomic site where the medication first enters the body.</t>
+    <t>薬が最初に体に入る解剖学的部位のコード化された仕様。 / A coded specification of the anatomic site where the medication first enters the body.</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationBodySiteJAMIExternal_VS</t>
@@ -1720,7 +1731,7 @@
     <t>MedicationStatement.dosage.site.coding</t>
   </si>
   <si>
-    <t>Code defined by a terminology system</t>
+    <t>用語システムによって定義されたコード / Code defined by a terminology system</t>
   </si>
   <si>
     <t>MedicationStatement.dosage.site.text</t>
@@ -1736,7 +1747,7 @@
 【JP Core仕様】HL7表0162をベースにした投与経路コードを使用することが望ましいが、ローカルコードも使用可能。</t>
   </si>
   <si>
-    <t>A code specifying the route or physiological path of administration of a therapeutic agent into or onto a patient's body.</t>
+    <t>患者の体への、または患者の体内への治療剤の投与のルートまたは生理学的経路を指定するコード。 / A code specifying the route or physiological path of administration of a therapeutic agent into or onto a patient's body.</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationRouteHL70162_VS</t>
@@ -1871,16 +1882,16 @@
     <t>MedicationStatement.dosage.method.coding.system</t>
   </si>
   <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+    <t>用語システムのアイデンティティ / Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>コード内のシンボルの意味を定義するコードシステムの識別。 / The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>uriは、oid（urn：oid：...）またはuuid（urn：uuid：...）である場合があります。OIDとUUIDは、HL7 OIDレジストリへの参照となります。それ以外の場合、URIは、FHIRの特別なURIを定義したHL7のリストから来るか、システムを明確かつ明確に確立する定義を参照する必要があります。 / The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>シンボルの定義のソースについて明確である必要があります。 / Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
     <t>http://jami.jp/CodeSystem/MedicationMethodBasicUsage</t>
@@ -1901,13 +1912,13 @@
     <t>MedicationStatement.dosage.method.coding.version</t>
   </si>
   <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+    <t>システムのバージョン - 関連する場合 / Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>このコードを選択するときに使用されたコードシステムのバージョン。コードの意味がバージョン全体で一貫しているため、適切にメンテナンスしたコードシステムでは報告されたバージョンを必要としないことに注意してください。ただし、これは一貫して保証することはできず、意味が一貫していることが保証されていない場合、バージョンを交換する必要があります。 / The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>用語がコードシステムバージョンを識別するために使用する文字列を明確に定義していない場合、推奨は、そのバージョンがバージョンの日付として公式に公開された日付（FHIR日付形式で表現）を使用することです。 / Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
   </si>
   <si>
     <t>Coding.version</t>
@@ -1925,13 +1936,13 @@
     <t>MedicationStatement.dosage.method.coding.code</t>
   </si>
   <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
+    <t>システムによって定義された構文のシンボル / Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>システムによって定義された構文のシンボル。シンボルは、定義されたコードまたはコーディングシステムによって定義された構文の式（例：調整後）である場合があります。 / A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>システム内の特定のコードを参照する必要があります。 / Need to refer to a particular code in the system.</t>
   </si>
   <si>
     <t>Coding.code</t>
@@ -1949,13 +1960,13 @@
     <t>MedicationStatement.dosage.method.coding.display</t>
   </si>
   <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+    <t>システムによって定義された表現 / Representation defined by the system</t>
+  </si>
+  <si>
+    <t>システムのルールに従って、システム内のコードの意味の表現。 / A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>システムを知らない読者のために、コードの人間の読み取り可能な意味を持ち込むことができる必要があります。 / Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
   </si>
   <si>
     <t>Coding.display</t>
@@ -1973,16 +1984,16 @@
     <t>MedicationStatement.dosage.method.coding.userSelected</t>
   </si>
   <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+    <t>このコーディングがユーザーによって直接選択された場合 / If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>このコーディングがユーザーによって直接選択されたことを示します。利用可能なアイテムのピックリスト（コードまたはディスプレイ）。 / Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>一連の代替案の中で、直接選択されたコードが新しい翻訳の最も適切な出発点です。この要素の使用とその結果をより完全に明確にするためには、「直接選択された」ことについては曖昧さがあり、取引パートナー契約が必要になる場合があります。 / Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>これは、臨床安全基準として特定されています - この正確なシステム/コードペアは、いくつかのルールまたは言語処理に基づいてシステムによって推測されるのではなく、明示的に選択されたことです。 / This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
   </si>
   <si>
     <t>Coding.userSelected</t>
@@ -2048,7 +2059,7 @@
     <t>Dosage.doseAndRate</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+    <t xml:space="preserve">ele-1:空のParametersリソースでない限り、すべてのFHIR要素には@valueまたはchildrenが必要です / All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
 </t>
   </si>
   <si>
@@ -2099,7 +2110,7 @@
 【JP Core仕様】1回の投与量（体積）を指定する。単位はUCUMを使用する。</t>
   </si>
   <si>
-    <t>The amount of therapeutic or other substance given at one administration event.</t>
+    <t>1つの投与イベントで与えられた治療またはその他の物質の量。 / The amount of therapeutic or other substance given at one administration event.</t>
   </si>
   <si>
     <t>Dosage.doseAndRate.dose[x]</t>
@@ -2121,12 +2132,14 @@
     <t>薬剤が投与される量の速度</t>
   </si>
   <si>
-    <t>It is possible to supply both a rate and a doseQuantity to provide full details about how the medication is to be administered and supplied. If the rate is intended to change over time, depending on local rules/regulations, each change should be captured as a new version of the MedicationRequest with an updated rate, or captured with a new MedicationRequest with the new rate.+    <t>レートとデスケーティティの両方を供給して、薬の投与と供給の方法についての詳細を提供することができます。レートが時間の経過とともに変化することを目的としている場合、ローカルのルール/規制に応じて、各変更は、更新されたレートのある薬物療法の新しいバージョンとしてキャプチャするか、新しいレートで新しい薬物採取でキャプチャされる必要があります。++レート（100 ml/hour）を使用して、時間の経過とともにレートを指定することができます。RateQuantityアプローチでは、時間が分母として指定されている特定の比率ではなく、ML/時間が含まれているUCUMグラマーを解析する機能をシステムに持つ必要があります。2時間にわたって500mlなどのレートが指定されている場合、250 mg/時のレートの量を使用して指定するよりも、定量的に正しい場合があります。 / It is possible to supply both a rate and a doseQuantity to provide full details about how the medication is to be administered and supplied. If the rate is intended to change over time, depending on local rules/regulations, each change should be captured as a new version of the MedicationRequest with an updated rate, or captured with a new MedicationRequest with the new rate.  It is possible to specify a rate over time (for example, 100 ml/hour) using either the rateRatio and rateQuantity.  The rateQuantity approach requires systems to have the capability to parse UCUM grammer where ml/hour is included rather than a specific ratio where the time is specified as the denominator.  Where a rate such as 500ml over 2 hours is specified, the use of rateRatio may be more semantically correct than specifying using a rateQuantity of 250 mg/hour.</t>
   </si>
   <si>
-    <t>Identifies the speed with which the medication was or will be introduced into the patient. Typically the rate for an infusion e.g. 100 ml per 1 hour or 100 ml/hr.  May also be expressed as a rate per unit of time e.g. 500 ml per 2 hours.   Other examples: 200 mcg/min or 200 mcg/1 minute; 1 liter/8 hours.  Sometimes, a rate can imply duration when expressed as total volume / duration (e.g.  500mL/2 hours implies a duration of 2 hours).  However, when rate doesn't imply duration (e.g. 250mL/hour), then the timing.repeat.duration is needed to convey the infuse over time period.</t>
+    <t>薬剤が患者に投与された速度または投与される速度を識別します。通常、輸液の場合は1時間あたり100mlまたは100ml/hrなどの速度です。時間の単位あたりの速度として表現することもできます（例：2時間あたり500ml）。その他の例：200 mcg/分または200 mcg/1分、1リットル/8時間。場合によっては、速度が総量/期間として表現される場合、期間を暗示することがあります（例：500mL/2時間は2時間の期間を暗示）。ただし、速度が期間を暗示しない場合（例：250mL/時間）、timing.repeat.durationが注入期間を伝えるために必要です。 / Identifies the speed with which the medication was or will be introduced into the patient. Typically the rate for an infusion e.g. 100 ml per 1 hour or 100 ml/hr.  May also be expressed as a rate per unit of time e.g. 500 ml per 2 hours.   Other examples: 200 mcg/min or 200 mcg/1 minute; 1 liter/8 hours.  Sometimes, a rate can imply duration when expressed as total volume / duration (e.g.  500mL/2 hours implies a duration of 2 hours).  However, when rate doesn't imply duration (e.g. 250mL/hour), then the timing.repeat.duration is needed to convey the infuse over time period.</t>
   </si>
   <si>
     <t>closed</t>
@@ -2180,10 +2193,10 @@
     <t>単位時間当たりの投薬量の上限</t>
   </si>
   <si>
-    <t>This is intended for use as an adjunct to the dosage when there is an upper cap.  For example "2 tablets every 4 hours to a maximum of 8/day".</t>
-  </si>
-  <si>
-    <t>The maximum total quantity of a therapeutic substance that may be administered to a subject over the period of time.  For example, 1000mg in 24 hours.</t>
+    <t>これは、上限があるときに投与量の補助として使用することを目的としています。たとえば、「4時間ごとに最大8時間あたり2錠」。 / This is intended for use as an adjunct to the dosage when there is an upper cap.  For example "2 tablets every 4 hours to a maximum of 8/day".</t>
+  </si>
+  <si>
+    <t>期間にわたって被験者に投与される可能性のある治療物質の最大総量。たとえば、24時間で1000mg。 / The maximum total quantity of a therapeutic substance that may be administered to a subject over the period of time.  For example, 1000mg in 24 hours.</t>
   </si>
   <si>
     <t>Dosage.maxDosePerPeriod</t>
@@ -2201,10 +2214,10 @@
     <t>1回あたりの投薬量の上限</t>
   </si>
   <si>
-    <t>This is intended for use as an adjunct to the dosage when there is an upper cap.  For example, a body surface area related dose with a maximum amount, such as 1.5 mg/m2 (maximum 2 mg) IV over 5 – 10 minutes would have doseQuantity of 1.5 mg/m2 and maxDosePerAdministration of 2 mg.</t>
-  </si>
-  <si>
-    <t>The maximum total quantity of a therapeutic substance that may be administered to a subject per administration.</t>
+    <t>これは、上限があるときに投与量の補助として使用することを目的としています。たとえば、5〜10分間で1.5 mg/m2（最大2 mg）IVなどの最大量の体積領域に関連する用量に関連する用量は、1.5 mg/m2、最大2 mgのDosequantityになります。 / This is intended for use as an adjunct to the dosage when there is an upper cap.  For example, a body surface area related dose with a maximum amount, such as 1.5 mg/m2 (maximum 2 mg) IV over 5 – 10 minutes would have doseQuantity of 1.5 mg/m2 and maxDosePerAdministration of 2 mg.</t>
+  </si>
+  <si>
+    <t>投与ごとの被験者に投与される可能性のある治療物質の最大総量。 / The maximum total quantity of a therapeutic substance that may be administered to a subject per administration.</t>
   </si>
   <si>
     <t>Dosage.maxDosePerAdministration</t>
@@ -2219,7 +2232,7 @@
     <t>生涯の投薬量の上限</t>
   </si>
   <si>
-    <t>The maximum total quantity of a therapeutic substance that may be administered per lifetime of the subject.</t>
+    <t>被験者の寿命ごとに投与される可能性のある治療物質の最大総量。 / The maximum total quantity of a therapeutic substance that may be administered per lifetime of the subject.</t>
   </si>
   <si>
     <t>Dosage.maxDosePerLifetime</t>
@@ -2555,7 +2568,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="106.38671875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="161.6796875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="66.17578125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
